--- a/data/1st Round/Corrected/CdS1_Results Table.xlsx
+++ b/data/1st Round/Corrected/CdS1_Results Table.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:T29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Rseriescm2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Rshuntcm2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -547,9 +557,6 @@
       <c r="L2" t="n">
         <v>0.00011993</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>18.984</v>
       </c>
@@ -563,6 +570,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S2" t="n">
+        <v>50.31773125721282</v>
+      </c>
+      <c r="T2" t="n">
+        <v>58.16303591796542</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -603,9 +616,6 @@
       <c r="L3" t="n">
         <v>0.00011947</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>18.982</v>
       </c>
@@ -619,6 +629,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S3" t="n">
+        <v>50.14913790043207</v>
+      </c>
+      <c r="T3" t="n">
+        <v>59.696723746163</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -659,9 +675,6 @@
       <c r="L4" t="n">
         <v>0.00014588</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>19.058</v>
       </c>
@@ -675,6 +688,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S4" t="n">
+        <v>52.98103497810289</v>
+      </c>
+      <c r="T4" t="n">
+        <v>48.99138618397148</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -715,9 +734,6 @@
       <c r="L5" t="n">
         <v>0.00013801</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>18.984</v>
       </c>
@@ -731,6 +747,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S5" t="n">
+        <v>53.99936453510902</v>
+      </c>
+      <c r="T5" t="n">
+        <v>47.27310304452644</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -771,9 +793,6 @@
       <c r="L6" t="n">
         <v>0.0002009</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>19.067</v>
       </c>
@@ -787,6 +806,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S6" t="n">
+        <v>48.37112716075483</v>
+      </c>
+      <c r="T6" t="n">
+        <v>46.59897182106366</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -827,9 +852,6 @@
       <c r="L7" t="n">
         <v>8.927e-05</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>18.972</v>
       </c>
@@ -843,6 +865,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S7" t="n">
+        <v>120.8562927047164</v>
+      </c>
+      <c r="T7" t="n">
+        <v>90.12288466003456</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -883,9 +911,6 @@
       <c r="L8" t="n">
         <v>6.719999999999999e-05</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>19.067</v>
       </c>
@@ -899,6 +924,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S8" t="n">
+        <v>147.059410296244</v>
+      </c>
+      <c r="T8" t="n">
+        <v>117.1525748249155</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -939,9 +970,6 @@
       <c r="L9" t="n">
         <v>0.00010653</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>18.984</v>
       </c>
@@ -955,6 +983,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S9" t="n">
+        <v>87.74958359122506</v>
+      </c>
+      <c r="T9" t="n">
+        <v>73.55430251790206</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -995,9 +1029,6 @@
       <c r="L10" t="n">
         <v>0.00010662</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>18.968</v>
       </c>
@@ -1011,6 +1042,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S10" t="n">
+        <v>73.88190560059991</v>
+      </c>
+      <c r="T10" t="n">
+        <v>64.72178314995698</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1051,9 +1088,6 @@
       <c r="L11" t="n">
         <v>0.00010158</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>19.067</v>
       </c>
@@ -1067,6 +1101,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S11" t="n">
+        <v>69.8492764284665</v>
+      </c>
+      <c r="T11" t="n">
+        <v>91.00252903417459</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1107,9 +1147,6 @@
       <c r="L12" t="n">
         <v>5.668e-05</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>18.985</v>
       </c>
@@ -1123,6 +1160,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S12" t="n">
+        <v>113.8937896462192</v>
+      </c>
+      <c r="T12" t="n">
+        <v>115.709419829221</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1163,9 +1206,6 @@
       <c r="L13" t="n">
         <v>5.542e-05</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>18.984</v>
       </c>
@@ -1179,6 +1219,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S13" t="n">
+        <v>71.78516768688978</v>
+      </c>
+      <c r="T13" t="n">
+        <v>58.17703057412109</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1219,9 +1265,6 @@
       <c r="L14" t="n">
         <v>5.536e-05</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>18.971</v>
       </c>
@@ -1235,6 +1278,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S14" t="n">
+        <v>76.44745126447276</v>
+      </c>
+      <c r="T14" t="n">
+        <v>62.45369641003493</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1275,9 +1324,6 @@
       <c r="L15" t="n">
         <v>2.592e-05</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>18.964</v>
       </c>
@@ -1291,6 +1337,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S15" t="n">
+        <v>64.49375766085042</v>
+      </c>
+      <c r="T15" t="n">
+        <v>58.29674552843818</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1331,9 +1383,6 @@
       <c r="L16" t="n">
         <v>4.768e-05</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>18.957</v>
       </c>
@@ -1347,6 +1396,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S16" t="n">
+        <v>186.3318162347515</v>
+      </c>
+      <c r="T16" t="n">
+        <v>132.693761082258</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1387,9 +1442,6 @@
       <c r="L17" t="n">
         <v>9.214e-05</v>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>19.067</v>
       </c>
@@ -1403,6 +1455,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S17" t="n">
+        <v>63.9172556327903</v>
+      </c>
+      <c r="T17" t="n">
+        <v>47.00196576708163</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1443,9 +1501,6 @@
       <c r="L18" t="n">
         <v>5.419e-05</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>18.981</v>
       </c>
@@ -1459,6 +1514,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S18" t="n">
+        <v>51.34295138432223</v>
+      </c>
+      <c r="T18" t="n">
+        <v>42.32023924714612</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1499,9 +1560,6 @@
       <c r="L19" t="n">
         <v>8.041e-05</v>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>18.958</v>
       </c>
@@ -1515,6 +1573,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S19" t="n">
+        <v>69.61013077141411</v>
+      </c>
+      <c r="T19" t="n">
+        <v>52.03130032093804</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1555,9 +1619,6 @@
       <c r="L20" t="n">
         <v>6.933e-05</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>18.958</v>
       </c>
@@ -1571,6 +1632,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S20" t="n">
+        <v>86.28525353813517</v>
+      </c>
+      <c r="T20" t="n">
+        <v>71.3408505026631</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1611,9 +1678,6 @@
       <c r="L21" t="n">
         <v>7.431e-05</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>18.958</v>
       </c>
@@ -1627,6 +1691,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S21" t="n">
+        <v>66.25735524568201</v>
+      </c>
+      <c r="T21" t="n">
+        <v>51.72019383735951</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1667,9 +1737,6 @@
       <c r="L22" t="n">
         <v>7.457e-05</v>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>18.956</v>
       </c>
@@ -1683,6 +1750,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S22" t="n">
+        <v>66.83343195168955</v>
+      </c>
+      <c r="T22" t="n">
+        <v>51.7186250379833</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1723,9 +1796,6 @@
       <c r="L23" t="n">
         <v>7.202000000000001e-05</v>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>18.956</v>
       </c>
@@ -1739,6 +1809,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S23" t="n">
+        <v>84.35976969349777</v>
+      </c>
+      <c r="T23" t="n">
+        <v>69.40936908332344</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1779,9 +1855,6 @@
       <c r="L24" t="n">
         <v>8.441999999999999e-05</v>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
         <v>18.983</v>
       </c>
@@ -1795,6 +1868,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S24" t="n">
+        <v>69.83347956847352</v>
+      </c>
+      <c r="T24" t="n">
+        <v>51.25308542623718</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1835,9 +1914,6 @@
       <c r="L25" t="n">
         <v>5.714e-05</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
         <v>18.982</v>
       </c>
@@ -1851,6 +1927,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S25" t="n">
+        <v>52.77456091442747</v>
+      </c>
+      <c r="T25" t="n">
+        <v>41.13036820845897</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1891,9 +1973,6 @@
       <c r="L26" t="n">
         <v>9.894e-05</v>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
         <v>19.057</v>
       </c>
@@ -1907,7 +1986,14 @@
           <t>01/22/2026</t>
         </is>
       </c>
-    </row>
+      <c r="S26" t="n">
+        <v>59.06764410280962</v>
+      </c>
+      <c r="T26" t="n">
+        <v>42.93647957563869</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
